--- a/public/templates/mau-lop-hoc.xlsx
+++ b/public/templates/mau-lop-hoc.xlsx
@@ -499,7 +499,7 @@
         <v>RECRUITING</v>
       </c>
       <c r="P2" t="str">
-        <v>Lớp khai trương — chương trình 20 suất miễn phí</v>
+        <v>Lớp khai trương — chương trình 24 suất miễn phí</v>
       </c>
       <c r="Q2" t="str">
         <v>Campaign launch 2026-05-23 tại 211 Nguyễn Hữu Thọ</v>
